--- a/Git_WE_KiCad_Released_Series_List.xlsx
+++ b/Git_WE_KiCad_Released_Series_List.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A401"/>
+  <dimension ref="A1:A403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1943,1293 +1943,1307 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>WE-SPC</t>
+          <t>WE-SLSP</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>WE-TCI</t>
+          <t>WE-SPC</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>WE-TDC</t>
+          <t>WE-TCI</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>WE-TDCHV</t>
+          <t>WE-TDC</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>WE-TFC</t>
+          <t>WE-TDCHV</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>WE-TI</t>
+          <t>WE-TFC</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>WE-TIHV</t>
+          <t>WE-TI</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>WE-TIS</t>
+          <t>WE-TIHV</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WE-TORPFC</t>
+          <t>WE-TIS</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>WE-TPB</t>
+          <t>WE-TORPFC</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WE-TPBHV</t>
+          <t>WE-TPB</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>WE-TPC</t>
+          <t>WE-TPBHV</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>WE-UCF</t>
+          <t>WE-TPC</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>WE-WPCC</t>
+          <t>WE-UCF</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>WE-XHMA</t>
+          <t>WE-WPCC</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>WE-XHMI</t>
+          <t>WE-XHMA</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WL-SDCB</t>
+          <t>WE-XHMI</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WL-SDSB</t>
+          <t>WL-SDCB</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WL-SICW</t>
+          <t>WL-SDSB</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WL-SIMW</t>
+          <t>WL-SICW</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WL-SIQW</t>
+          <t>WL-SIMW</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WL-SIRW</t>
+          <t>WL-SIQW</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>WL-SISW</t>
+          <t>WL-SIRW</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>WL-SITW</t>
+          <t>WL-SISW</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>WL-STCB</t>
+          <t>WL-SITW</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>WL-STCW</t>
+          <t>WL-STCB</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>WL-STRB</t>
+          <t>WL-STCW</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>WL-STSB</t>
+          <t>WL-STRB</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>WL-STSW</t>
+          <t>WL-STSB</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>WL-STTB</t>
+          <t>WL-STSW</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>WL-STTW</t>
+          <t>WL-STTB</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>WL-TDRB</t>
+          <t>WL-STTW</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>WL-TDRW</t>
+          <t>WL-TDRB</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>WL-TIRC</t>
+          <t>WL-TDRW</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>WL-TIRW</t>
+          <t>WL-TIRC</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>WL-TTRB</t>
+          <t>WL-TIRW</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>WL-TTRW</t>
+          <t>WL-TTRB</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>WL-VCSL</t>
+          <t>WL-TTRW</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>WL-SBCC</t>
+          <t>WL-VCSL</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>WL-SBCD</t>
+          <t>WL-SBCC</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>WL-SBCW</t>
+          <t>WL-SBCD</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>WL-SBRW</t>
+          <t>WL-SBCW</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>WL-SBSW</t>
+          <t>WL-SBRW</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>WL-SBTW</t>
+          <t>WL-SBSW</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>WL-SFCC</t>
+          <t>WL-SBTW</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>WL-SFCD</t>
+          <t>WL-SFCC</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>WL-SFCW</t>
+          <t>WL-SFCD</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>WL-SFRW</t>
+          <t>WL-SFCW</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>WL-SFSW</t>
+          <t>WL-SFRW</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>WL-SFTD</t>
+          <t>WL-SFSW</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>WL-SFTW</t>
+          <t>WL-SFTD</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>WL-SMCC</t>
+          <t>WL-SFTW</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>WL-SMCD</t>
+          <t>WL-SMCC</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>WL-SMCW</t>
+          <t>WL-SMCD</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>WL-SMDC</t>
+          <t>WL-SMCW</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>WL-SMRD</t>
+          <t>WL-SMDC</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>WL-SMRW</t>
+          <t>WL-SMRD</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>WL-SMSW</t>
+          <t>WL-SMRW</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>WL-SMTD</t>
+          <t>WL-SMSW</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>WL-SMTW</t>
+          <t>WL-SMTD</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>WL-SWTC</t>
+          <t>WL-SMTW</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>WL-SWTP</t>
+          <t>WL-SWTC</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>WL-TMRC</t>
+          <t>WL-SWTP</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>WL-TMRW</t>
+          <t>WL-TMRC</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>WPME-CDI2C</t>
+          <t>WL-TMRW</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>WPME-CDIP</t>
+          <t>WPME-CDI2C</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>WPME-CDIS</t>
+          <t>WPME-CDIP</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>WPME-FDSM</t>
+          <t>WPME-CDIS</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>WPME-FIMM</t>
+          <t>WPME-FDSM</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>WPME-FIRM</t>
+          <t>WPME-FIMM</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>WPME-FISM</t>
+          <t>WPME-FIRM</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>WPME-LDHM</t>
+          <t>WPME-FISM</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>WPME-VDLM</t>
+          <t>WPME-LDHM</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>WPME-VDMM</t>
+          <t>WPME-VDLM</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>WPME-VDRM</t>
+          <t>WPME-VDMM</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>WPME-VISM</t>
+          <t>WPME-VDRM</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>WL-OSEN</t>
+          <t>WPME-VISM</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>WL-OCDA</t>
+          <t>WL-OSEN</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>WL-OCHS</t>
+          <t>WL-OCDA</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>WL-OCPT</t>
+          <t>WL-OCHS</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>WL-OCTR</t>
+          <t>WL-OCPT</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>WIRL</t>
+          <t>WL-OCTR</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>WP-BUCF</t>
+          <t>WIRL</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>WP-BUFU</t>
+          <t>WP-BUCF</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>WP-BUTR</t>
+          <t>WP-BUFU</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>WP-PFEFUA</t>
+          <t>WP-BUTR</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>WP-PFICFA</t>
+          <t>WP-PFEFUA</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>WP-PFIFUA</t>
+          <t>WP-PFICFA</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>WP-PLUG</t>
+          <t>WP-PFIFUA</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>WP-RAFE</t>
+          <t>WP-PLUG</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>WP-RAFU</t>
+          <t>WP-RAFE</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>WP-RATR</t>
+          <t>WP-RAFU</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>WP-SHFU</t>
+          <t>WP-RATR</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>WP-SMBU</t>
+          <t>WP-SHFU</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>WP-SMRA</t>
+          <t>WP-SMBU</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>WP-SMRT</t>
+          <t>WP-SMRA</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>WP-SMSH</t>
+          <t>WP-SMRT</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>WP-TGCF</t>
+          <t>WP-SMSH</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>WP-TGTR</t>
+          <t>WP-TGCF</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>WP-THRBU</t>
+          <t>WP-TGTR</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>WP-THRSH</t>
+          <t>WP-THRBU</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>WRIS-KSKE</t>
+          <t>WP-THRSH</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>WRIS-KWKB</t>
+          <t>WRIS-KSKE</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>WRIS-KWKH</t>
+          <t>WRIS-KWKB</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>WRIS-PSMB</t>
+          <t>WRIS-KWKH</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>WRIS-PSMC</t>
+          <t>WRIS-PSMB</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>WRIS-RSKS</t>
+          <t>WRIS-PSMC</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>WE-RCDS</t>
+          <t>WRIS-RSKS</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>WE-SCFA</t>
+          <t>WE-RCDS</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>WE-SECF</t>
+          <t>WE-SCFA</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>WE-SHC</t>
+          <t>WE-SECF</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>WE-SMGS</t>
+          <t>WE-SHC</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>WS-DESU</t>
+          <t>WE-SHCA</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>WS-DESV</t>
+          <t>WE-SMGS</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>WS-DISV</t>
+          <t>WS-DESU</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>WS-DITU</t>
+          <t>WS-DESV</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>WS-DITV</t>
+          <t>WS-DISV</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>WS-ENTV</t>
+          <t>WS-DITU</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>WS-MITV</t>
+          <t>WS-DITV</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>WS-PBSU</t>
+          <t>WS-ENTV</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>WS-PBTL</t>
+          <t>WS-MITV</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>WS-PBTU</t>
+          <t>WS-PBSU</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>WS-PBTV</t>
+          <t>WS-PBTL</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>WS-ROSV</t>
+          <t>WS-PBTU</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>WS-ROTU</t>
+          <t>WS-PBTV</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>WS-ROTV</t>
+          <t>WS-ROSV</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>WS-RPTL</t>
+          <t>WS-ROTU</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>WS-RSTV</t>
+          <t>WS-ROTV</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>WS-SLSU</t>
+          <t>WS-RPTL</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>WS-SLSV</t>
+          <t>WS-RSTV</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>WS-SLTU</t>
+          <t>WS-SLSU</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>WS-SLTV</t>
+          <t>WS-SLSV</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>WS-TASL</t>
+          <t>WS-SLTU</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>WS-TASU</t>
+          <t>WS-SLTV</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>WS-TASV</t>
+          <t>WS-TASL</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>WS-TATL</t>
+          <t>WS-TASU</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>WS-TATU</t>
+          <t>WS-TASV</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>WS-TATV</t>
+          <t>WS-TATL</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>WS-TOTV</t>
+          <t>WS-TATU</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>WE-AGDA</t>
+          <t>WS-TATV</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>WE-AGDT</t>
+          <t>WS-TOTV</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>WE-BMS</t>
+          <t>WE-AGDA</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>WE-CST</t>
+          <t>WE-AGDT</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>WE-CSTLF</t>
+          <t>WE-BMS</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>WE-FB</t>
+          <t>WE-CST</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>WE-FB3751</t>
+          <t>WE-CSTLF</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>WE-FLEX+</t>
+          <t>WE-FB</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>WE-FLEX</t>
+          <t>WE-FB3751</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>WE-FLEXHV</t>
+          <t>WE-FLEX+</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>WE-FLYLT</t>
+          <t>WE-FLEX</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>WE-FLYTI</t>
+          <t>WE-FLEXHV</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>WE-GDT</t>
+          <t>WE-FLYLT</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>WE-GDTI</t>
+          <t>WE-FLYTI</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>WE-IBTI</t>
+          <t>WE-GDT</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>WE-LAN</t>
+          <t>WE-GDTI</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>WE-LAN10G</t>
+          <t>WE-IBTI</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>WE-LANAQ</t>
+          <t>WE-LAN</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>WE-LANMX</t>
+          <t>WE-LAN10G</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>WE-LLCR</t>
+          <t>WE-LANAQ</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>WE-OLEE</t>
+          <t>WE-LANMX</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>WE-OLEFD</t>
+          <t>WE-LLCR</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>WE-OLLT</t>
+          <t>WE-OLEE</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>WE-OLPI</t>
+          <t>WE-OLEFD</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>WE-OLRM</t>
+          <t>WE-OLLT</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>WE-OLSTM</t>
+          <t>WE-OLPI</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>WE-OLTI</t>
+          <t>WE-OLRM</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>WE-PFC</t>
+          <t>WE-OLSTM</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>WE-PLC</t>
+          <t>WE-OLTI</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>WE-PLN</t>
+          <t>WE-PFC</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>WE-PoE++</t>
+          <t>WE-PLC</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>WE-PoE+</t>
+          <t>WE-PLN</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>WE-PoE</t>
+          <t>WE-PoE++</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>WE-PoEH</t>
+          <t>WE-PoE+</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>WE-PPTI</t>
+          <t>WE-PoE</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>WE-PPTM</t>
+          <t>WE-PoEH</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>WE-PSPA</t>
+          <t>WE-PPTI</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>WE-RJ45LAN</t>
+          <t>WE-PPTM</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>WE-SPE</t>
+          <t>WE-PSPA</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>WE-STST</t>
+          <t>WE-RJ45LAN</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>WE-UNIT</t>
+          <t>WE-SPE</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>WE-UOST</t>
+          <t>WE-STST</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>WL-SUMW</t>
+          <t>WE-UNIT</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>WL-SUTW</t>
+          <t>WE-UOST</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>WE-VD</t>
+          <t>WL-SUMW</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
+        <is>
+          <t>WL-SUTW</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>WE-VD</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>WE-VS</t>
         </is>
